--- a/jogos_2024-12-28.xlsx
+++ b/jogos_2024-12-28.xlsx
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.58</v>
+        <v>2.18</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.39</v>
+        <v>3.02</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>1.33</v>
       </c>
-      <c r="S4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.43</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.25</v>
       </c>
-      <c r="X4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['35', '72', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45654.22916666666</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="M5" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.02</v>
+        <v>2.39</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['35', '72', '79']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.98</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['24']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45654.22916666666</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
         <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="U8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['22', '24']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['11', '90+3']</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
         <v>1.17</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['26', '35']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['24', '55']</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45654.41666666666</v>
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Tataouine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.2</v>
       </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
       <c r="O9" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
         <v>1.62</v>
@@ -1596,59 +1596,59 @@
         <v>2.15</v>
       </c>
       <c r="T9" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
         <v>2.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="Z9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['14', '74', '87']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA9" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['22', '24']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['11', '90+3']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AI9" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45654.41666666666</v>
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tataouine</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
         <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['26', '35']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['24', '55']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.62</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['14', '74', '87']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45654.41666666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,109 +2062,109 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>3.79</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="P13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>4</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="X13" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.8</v>
+        <v>2.59</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['56', '90+8']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['45', '52']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45654.45833333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,20 +2320,20 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
         <v>1</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
         <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.43</v>
+        <v>1.97</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['56', '90+8']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45654.45833333334</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,22 +2475,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="M16" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="N16" t="n">
-        <v>3.79</v>
+        <v>3.03</v>
       </c>
       <c r="O16" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
         <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
         <v>1.62</v>
@@ -2508,16 +2508,16 @@
         <v>1.11</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="X16" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AA16" t="n">
         <v>5.2</v>
@@ -2526,32 +2526,32 @@
         <v>1.14</v>
       </c>
       <c r="AC16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['45', '52']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>3.2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45654.45833333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X18" t="n">
         <v>2.88</v>
       </c>
-      <c r="N18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="Y18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.62</v>
       </c>
-      <c r="S18" t="n">
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH18" t="n">
         <v>2.2</v>
       </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['14']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AI18" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45654.5</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z19" t="n">
         <v>1.83</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['7', '47']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI19" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA19" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['13', '15', '81']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['31', '73']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45654.5</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
         <v>2</v>
       </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="X20" t="n">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.14</v>
+        <v>3.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['7', '47']</t>
+          <t>['13', '15', '81']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['31', '73']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45654.5</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,23 +3094,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>2</v>
-      </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
@@ -3120,55 +3120,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X21" t="n">
         <v>2.3</v>
       </c>
-      <c r="O21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.56</v>
-      </c>
       <c r="Y21" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.2</v>
+        <v>5.45</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
         <v>2.1</v>
@@ -3178,25 +3178,25 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['7', '28']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45654.5</v>
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V22" t="n">
         <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="X22" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Z22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['7', '28']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>3.5</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45654.5</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
         <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V23" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="X23" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AA23" t="n">
         <v>4.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.38</v>
+        <v>1.06</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="AI23" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45654.52083333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="P24" t="n">
         <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="X24" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AA24" t="n">
         <v>4.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45654.52083333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>SuperSport United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N29" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O29" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P29" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="S29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X29" t="n">
         <v>2.35</v>
       </c>
-      <c r="T29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V29" t="n">
+      <c r="Y29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.1</v>
       </c>
-      <c r="W29" t="n">
+      <c r="AC29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.48</v>
       </c>
-      <c r="X29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['22', '45+3']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['2', '57']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45654.625</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SuperSport United</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="M30" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O30" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P30" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="S30" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U30" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X30" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AA30" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['22', '45+3']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['2', '57']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45654.625</v>
